--- a/data/trending_integrated_20260923_11.xlsx
+++ b/data/trending_integrated_20260923_11.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31238348558</v>
+        <v>31278449633</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -619,7 +619,7 @@
         <v>1809</v>
       </c>
       <c r="R2" t="n">
-        <v>-1000</v>
+        <v>-3000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18140</v>
+        <v>19070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.88%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15520</v>
+        <v>16540</v>
       </c>
       <c r="K3" t="n">
-        <v>15800</v>
+        <v>17530</v>
       </c>
       <c r="L3" t="n">
-        <v>19050</v>
+        <v>19950</v>
       </c>
       <c r="M3" t="n">
-        <v>15200</v>
+        <v>17500</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>54243491180</v>
+        <v>261520567830</v>
       </c>
       <c r="P3" t="n">
-        <v>34650</v>
+        <v>30550</v>
       </c>
       <c r="Q3" t="n">
-        <v>6980</v>
+        <v>6100</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-46000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X 선정 및 11조원 휴대용 X-Ray 시장 도전. NASA 우주 임무 적합 장비 선정.</t>
+          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 소식.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'X-Ray']</t>
+          <t>['양자', '아이온큐']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18790</v>
+        <v>17850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.60%</t>
+          <t>'+15.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="H4" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16540</v>
+        <v>15520</v>
       </c>
       <c r="K4" t="n">
-        <v>17530</v>
+        <v>15800</v>
       </c>
       <c r="L4" t="n">
-        <v>19950</v>
+        <v>19050</v>
       </c>
       <c r="M4" t="n">
-        <v>17500</v>
+        <v>15200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>250972158485</v>
+        <v>55869433605</v>
       </c>
       <c r="P4" t="n">
-        <v>30550</v>
+        <v>34650</v>
       </c>
       <c r="Q4" t="n">
-        <v>6100</v>
+        <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>118000</v>
+        <v>2000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 소식.</t>
+          <t>스페이스X 및 NASA 선정, 인도 수주 등 호재 기반 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자', '아이온큐']</t>
+          <t>['X-ray', '스페이스X', 'NASA']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14400</v>
+        <v>14380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.77%</t>
+          <t>'+10.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="H5" t="n">
         <v>0.86</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>120773566210</v>
+        <v>124525755065</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4040</v>
+        <v>3890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.46%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>52053408640</v>
+        <v>56338341436</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -987,14 +987,14 @@
         <v>1738</v>
       </c>
       <c r="R6" t="n">
-        <v>-78000</v>
+        <v>-41000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 급락 및 대규모 거래량 발생, 유증 관련 정보 공유.</t>
+          <t>급락 및 물량 떠넘기기에 대한 우려와 함께 전량 매도 의견 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유증', '도깨비', '거래량']</t>
+          <t>['주포', '유증']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218000</v>
+        <v>217500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H7" t="n">
         <v>75.51000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>574209798500</v>
+        <v>583882941750</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1079,10 +1079,10 @@
         <v>65000</v>
       </c>
       <c r="R7" t="n">
-        <v>276000</v>
+        <v>743000</v>
       </c>
       <c r="S7" t="n">
-        <v>-25000</v>
+        <v>-47000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>282250</v>
+        <v>282000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.08%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G8" t="n">
-        <v>2057</v>
+        <v>1925</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1162,7 +1162,7 @@
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2245584911750</v>
+        <v>2325921631500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1171,14 +1171,14 @@
         <v>82400</v>
       </c>
       <c r="R8" t="n">
-        <v>1308000</v>
+        <v>1732000</v>
       </c>
       <c r="S8" t="n">
-        <v>346000</v>
+        <v>499000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 35만원 목표 제시. JP모건의 HBM 1위 인정 소식 언급.</t>
+          <t>JP모건의 HBM 1위 인정 및 개인 매도 자제 시 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8610</v>
+        <v>13770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+1.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="H9" t="n">
-        <v>26.63</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8470</v>
+        <v>13600</v>
       </c>
       <c r="K9" t="n">
-        <v>8510</v>
+        <v>13750</v>
       </c>
       <c r="L9" t="n">
-        <v>8870</v>
+        <v>15050</v>
       </c>
       <c r="M9" t="n">
-        <v>8480</v>
+        <v>13740</v>
       </c>
       <c r="N9" t="n">
-        <v>26.58</v>
+        <v>9.77</v>
       </c>
       <c r="O9" t="n">
-        <v>16346352765</v>
+        <v>86680112090</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>23550</v>
       </c>
       <c r="Q9" t="n">
-        <v>8120</v>
+        <v>5780</v>
       </c>
       <c r="R9" t="n">
-        <v>359000</v>
+        <v>180000</v>
       </c>
       <c r="S9" t="n">
-        <v>23000</v>
+        <v>-194000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유리기판 사업 성장성 및 실적 개선 기대감, 외인 매수세 일부 유입.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유리기판', '실적', '외인']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13790</v>
+        <v>8570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.16</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="H10" t="n">
-        <v>9.609999999999999</v>
+        <v>26.63</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13600</v>
+        <v>8470</v>
       </c>
       <c r="K10" t="n">
-        <v>13750</v>
+        <v>8510</v>
       </c>
       <c r="L10" t="n">
-        <v>15050</v>
+        <v>8870</v>
       </c>
       <c r="M10" t="n">
-        <v>13750</v>
+        <v>8480</v>
       </c>
       <c r="N10" t="n">
-        <v>9.77</v>
+        <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>85304829060</v>
+        <v>17146452065</v>
       </c>
       <c r="P10" t="n">
-        <v>23550</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>5780</v>
+        <v>8120</v>
       </c>
       <c r="R10" t="n">
-        <v>275000</v>
+        <v>336000</v>
       </c>
       <c r="S10" t="n">
-        <v>-64000</v>
+        <v>-6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>유리기판 사업 성장성 및 실적 개선 기대감, 외인 매수세 일부 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['유리기판', '실적', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31650</v>
+        <v>31500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
         <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" t="n">
         <v>52.81</v>
@@ -1438,7 +1438,7 @@
         <v>25.75</v>
       </c>
       <c r="O11" t="n">
-        <v>72339023200</v>
+        <v>73675931675</v>
       </c>
       <c r="P11" t="n">
         <v>32100</v>
@@ -1447,10 +1447,10 @@
         <v>21000</v>
       </c>
       <c r="R11" t="n">
-        <v>29000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>51000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1846000</v>
+        <v>1842000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="G12" t="n">
-        <v>1582</v>
+        <v>1633</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1524,13 +1524,13 @@
         <v>1900000</v>
       </c>
       <c r="M12" t="n">
-        <v>1843000</v>
+        <v>1837000</v>
       </c>
       <c r="N12" t="n">
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>2413354694500</v>
+        <v>2598457917000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1539,23 +1539,23 @@
         <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>-28000</v>
+        <v>-100000</v>
       </c>
       <c r="S12" t="n">
-        <v>80000</v>
+        <v>106000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 신뢰도 저하 및 외인 매도 우려. 마이크론 반도체 상승세 언급.</t>
+          <t>국내 증시 및 외인 매도세에 대한 불신과 함께 상승 기대감 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '외인매도']</t>
+          <t>['외인', '국장']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2890</v>
+        <v>17630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'-1.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.92</v>
+        <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>135</v>
+        <v>612</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4</v>
+        <v>5.46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2885</v>
+        <v>17810</v>
       </c>
       <c r="K13" t="n">
-        <v>3000</v>
+        <v>17950</v>
       </c>
       <c r="L13" t="n">
-        <v>3480</v>
+        <v>18180</v>
       </c>
       <c r="M13" t="n">
-        <v>2860</v>
+        <v>17410</v>
       </c>
       <c r="N13" t="n">
-        <v>0.48</v>
+        <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>19250681998</v>
+        <v>112300140900</v>
       </c>
       <c r="P13" t="n">
-        <v>4760</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>973</v>
+        <v>1272</v>
       </c>
       <c r="R13" t="n">
-        <v>-235000</v>
+        <v>-260000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
+          <t>2만원 돌파 기대감 및 개인/외국인 매수세 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유상증자', '공매도', '차트분석']</t>
+          <t>['쇼티지', '광섬유']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17660</v>
+        <v>30500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.76</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="G14" t="n">
-        <v>586</v>
+        <v>1384</v>
       </c>
       <c r="H14" t="n">
-        <v>5.46</v>
+        <v>16.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17810</v>
+        <v>31050</v>
       </c>
       <c r="K14" t="n">
-        <v>17950</v>
+        <v>31300</v>
       </c>
       <c r="L14" t="n">
-        <v>18180</v>
+        <v>31550</v>
       </c>
       <c r="M14" t="n">
-        <v>17410</v>
+        <v>30050</v>
       </c>
       <c r="N14" t="n">
-        <v>6.22</v>
+        <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>110100937185</v>
+        <v>6840387100</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>-78000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감 및 쇼티지 현상 언급. 명절 전 거래일 주가 하락 가능성도 제기.</t>
+          <t>미국 릴레이테라퓨틱스 상승 및 FDA 승인 기대감 기반 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['쇼티지', '명절효과', '주포세력']</t>
+          <t>['FDA', '릴레이테라퓨틱스', '간암']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,169 +1752,169 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30500</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>218</v>
+        <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>1338</v>
+        <v>93</v>
       </c>
       <c r="H15" t="n">
-        <v>16.63</v>
+        <v>11.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>31050</v>
+        <v>31600</v>
       </c>
       <c r="K15" t="n">
-        <v>31300</v>
+        <v>32150</v>
       </c>
       <c r="L15" t="n">
-        <v>31550</v>
+        <v>32200</v>
       </c>
       <c r="M15" t="n">
-        <v>30050</v>
+        <v>30650</v>
       </c>
       <c r="N15" t="n">
-        <v>16.42</v>
+        <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>6507194950</v>
+        <v>57967905575</v>
       </c>
       <c r="P15" t="n">
-        <v>69200</v>
+        <v>75900</v>
       </c>
       <c r="Q15" t="n">
-        <v>24150</v>
+        <v>15000</v>
       </c>
       <c r="R15" t="n">
-        <v>-27000</v>
+        <v>-463000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>간암 리보 DP 및 담관암 결과 발표 기대. 릴레이테라퓨틱스 상승 및 FDA 허가 임박 전망.</t>
+          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙']</t>
+          <t>['구리', '텍사스', '가온전선']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30950</v>
+        <v>23200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
         <v>92</v>
       </c>
       <c r="H16" t="n">
-        <v>11.7</v>
+        <v>1.68</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31600</v>
+        <v>23950</v>
       </c>
       <c r="K16" t="n">
-        <v>32150</v>
+        <v>24400</v>
       </c>
       <c r="L16" t="n">
-        <v>32200</v>
+        <v>25700</v>
       </c>
       <c r="M16" t="n">
-        <v>30800</v>
+        <v>23050</v>
       </c>
       <c r="N16" t="n">
-        <v>11.3</v>
+        <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>54708532375</v>
+        <v>64890968000</v>
       </c>
       <c r="P16" t="n">
-        <v>75900</v>
+        <v>39350</v>
       </c>
       <c r="Q16" t="n">
-        <v>15000</v>
+        <v>8200</v>
       </c>
       <c r="R16" t="n">
-        <v>-295000</v>
+        <v>-39000</v>
       </c>
       <c r="S16" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
+          <t>타임지 '세계 최고 헬스테크 기업' 선정. 10만까지 상승 기대감 있으나 프로그램 매매 및 눌림목 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['구리', '텍사스', '가온전선']</t>
+          <t>['헬스테크', '타임지', '프로그램매매']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23225</v>
+        <v>2770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H17" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>23950</v>
+        <v>2885</v>
       </c>
       <c r="K17" t="n">
-        <v>24400</v>
+        <v>3000</v>
       </c>
       <c r="L17" t="n">
-        <v>25700</v>
+        <v>3480</v>
       </c>
       <c r="M17" t="n">
-        <v>23050</v>
+        <v>2770</v>
       </c>
       <c r="N17" t="n">
-        <v>1.76</v>
+        <v>0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>64442413875</v>
+        <v>19882929568</v>
       </c>
       <c r="P17" t="n">
-        <v>39350</v>
+        <v>4760</v>
       </c>
       <c r="Q17" t="n">
-        <v>8200</v>
+        <v>973</v>
       </c>
       <c r="R17" t="n">
-        <v>-37000</v>
+        <v>-227000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>타임지 '세계 최고 헬스테크 기업' 선정. 10만까지 상승 기대감 있으나 프로그램 매매 및 눌림목 언급.</t>
+          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '프로그램매매']</t>
+          <t>['유상증자', '공매도', '차트분석']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48750</v>
+        <v>48650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H18" t="n">
         <v>38.34</v>
@@ -2076,13 +2076,13 @@
         <v>51600</v>
       </c>
       <c r="M18" t="n">
-        <v>48650</v>
+        <v>48600</v>
       </c>
       <c r="N18" t="n">
         <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>60035233425</v>
+        <v>62071142725</v>
       </c>
       <c r="P18" t="n">
         <v>67300</v>
@@ -2091,23 +2091,23 @@
         <v>23150</v>
       </c>
       <c r="R18" t="n">
-        <v>-182000</v>
+        <v>-259000</v>
       </c>
       <c r="S18" t="n">
-        <v>-21000</v>
+        <v>-30000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5조 수주에도 주가 반응 없음. 20일선 지지선 이탈 및 박스권 움직임 언급.</t>
+          <t>주가 하락 및 횡보에 대한 불만과 함께 추가 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['LNG', '원전']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81700</v>
+        <v>81050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.55%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="F19" t="n">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="G19" t="n">
-        <v>1198</v>
+        <v>1260</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2168,13 +2168,13 @@
         <v>86100</v>
       </c>
       <c r="M19" t="n">
-        <v>81400</v>
+        <v>80800</v>
       </c>
       <c r="N19" t="n">
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>156724700050</v>
+        <v>172979943200</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2183,23 +2183,23 @@
         <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-248000</v>
+        <v>-474000</v>
       </c>
       <c r="S19" t="n">
-        <v>-42000</v>
+        <v>-68000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 한국형 원전 2기 확정 소식에도 주가 하락. SMR 및 트럼프 언급.</t>
+          <t>미국 원전 2기 확정 소식에도 불구하고 주가 하락 및 매도세 관측.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', 'SMR']</t>
+          <t>['원전', 'SMR', '외인']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17500</v>
+        <v>17400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.91%</t>
+          <t>'-7.45%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G20" t="n">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2260,13 +2260,13 @@
         <v>18800</v>
       </c>
       <c r="M20" t="n">
-        <v>17410</v>
+        <v>17380</v>
       </c>
       <c r="N20" t="n">
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>105164301805</v>
+        <v>110241634480</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2275,14 +2275,14 @@
         <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-1005000</v>
+        <v>-1845000</v>
       </c>
       <c r="S20" t="n">
-        <v>-51000</v>
+        <v>-250000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력 파산 주장 및 대차해지 운동 독려. 감사원 신고 심의 통과 소식.</t>
+          <t>공매도 세력의 파산 관련 언급 및 대차해지 운동 독려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>

--- a/data/trending_integrated_20260923_11.xlsx
+++ b/data/trending_integrated_20260923_11.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31278449633</v>
+        <v>31400819258</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19070</v>
+        <v>19040</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.30%</t>
+          <t>'+15.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>261520567830</v>
+        <v>264476456375</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 소식.</t>
+          <t>미국 양자 관련주 급등, 양자 보안 기술의 상용화 가능성과 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자', '아이온큐']</t>
+          <t>['양자', '보안', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17850</v>
+        <v>17810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.01%</t>
+          <t>'+14.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
         <v>0.6</v>
@@ -794,7 +794,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>55869433605</v>
+        <v>57126437100</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 인도 수주 등 호재 기반 주가 급등 전망.</t>
+          <t>스페이스X 및 NASA 선정, 11조원 휴대용 X-ray 시장 도전 및 인도발 수주 재료 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['X-ray', '스페이스X', 'NASA']</t>
+          <t>['X-ray', '스페이스X', '수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14380</v>
+        <v>14450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.62%</t>
+          <t>'+11.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
         <v>0.86</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>124525755065</v>
+        <v>125757818165</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3890</v>
+        <v>3895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.43%</t>
+          <t>'+4.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>56338341436</v>
+        <v>57781000754</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급락 및 물량 떠넘기기에 대한 우려와 함께 전량 매도 의견 표출.</t>
+          <t>급격한 하락과 물량 떠넘기기 의혹, 상폐 및 단기 거래장에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주포', '유증']</t>
+          <t>['급락', '물량', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H7" t="n">
         <v>75.51000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>583882941750</v>
+        <v>598145385500</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1079,7 +1079,7 @@
         <v>65000</v>
       </c>
       <c r="R7" t="n">
-        <v>743000</v>
+        <v>753000</v>
       </c>
       <c r="S7" t="n">
         <v>-47000</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>282000</v>
+        <v>281750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.99%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G8" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276500</v>
+        <v>275000</v>
       </c>
       <c r="K8" t="n">
-        <v>284500</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>285000</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>281000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2325921631500</v>
+        <v>2372301000000</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>82400</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1732000</v>
+        <v>1744000</v>
       </c>
       <c r="S8" t="n">
         <v>499000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JP모건의 HBM 1위 인정 및 개인 매도 자제 시 상승 전망.</t>
+          <t>JP모건의 HBM 1위 인정, 개인 매도 자제 시 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', 'JP모건']</t>
+          <t>['HBM', '배당', '상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13770</v>
+        <v>13890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.25%</t>
+          <t>'+2.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H9" t="n">
         <v>9.609999999999999</v>
@@ -1254,7 +1254,7 @@
         <v>9.77</v>
       </c>
       <c r="O9" t="n">
-        <v>86680112090</v>
+        <v>87871542715</v>
       </c>
       <c r="P9" t="n">
         <v>23550</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8570</v>
+        <v>8550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.18%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>17146452065</v>
+        <v>17629797400</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1355,7 +1355,7 @@
         <v>8120</v>
       </c>
       <c r="R10" t="n">
-        <v>336000</v>
+        <v>353000</v>
       </c>
       <c r="S10" t="n">
         <v>-6000</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31500</v>
+        <v>1844000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.62</v>
+        <v>-0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>507</v>
       </c>
       <c r="G11" t="n">
-        <v>116</v>
+        <v>1668</v>
       </c>
       <c r="H11" t="n">
-        <v>52.81</v>
+        <v>50.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>31400</v>
+        <v>1840000</v>
       </c>
       <c r="K11" t="n">
-        <v>31500</v>
+        <v>1899000</v>
       </c>
       <c r="L11" t="n">
-        <v>32100</v>
+        <v>1900000</v>
       </c>
       <c r="M11" t="n">
-        <v>31100</v>
+        <v>1837000</v>
       </c>
       <c r="N11" t="n">
-        <v>25.75</v>
+        <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>73675931675</v>
+        <v>2709575745500</v>
       </c>
       <c r="P11" t="n">
-        <v>32100</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>21000</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>-103000</v>
       </c>
       <c r="S11" t="n">
-        <v>51000</v>
+        <v>106000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>국내 증시 전반에 대한 불신과 외인 매도세 언급, 마이크론과의 비교.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,51 +1463,51 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['국장', '외인', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1842000</v>
+        <v>31450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>501</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>1633</v>
+        <v>120</v>
       </c>
       <c r="H12" t="n">
-        <v>50.15</v>
+        <v>52.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1840000</v>
+        <v>31400</v>
       </c>
       <c r="K12" t="n">
-        <v>1899000</v>
+        <v>31500</v>
       </c>
       <c r="L12" t="n">
-        <v>1900000</v>
+        <v>32100</v>
       </c>
       <c r="M12" t="n">
-        <v>1837000</v>
+        <v>31100</v>
       </c>
       <c r="N12" t="n">
-        <v>50.17</v>
+        <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2598457917000</v>
+        <v>75692210125</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>32100</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>21000</v>
       </c>
       <c r="R12" t="n">
-        <v>-100000</v>
+        <v>-6000</v>
       </c>
       <c r="S12" t="n">
-        <v>106000</v>
+        <v>51000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 및 외인 매도세에 대한 불신과 함께 상승 기대감 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,20 +1555,20 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인', '국장']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17630</v>
+        <v>17600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="H13" t="n">
         <v>5.46</v>
@@ -1622,7 +1622,7 @@
         <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>112300140900</v>
+        <v>115130435660</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30500</v>
+        <v>30650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.77%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F14" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="H14" t="n">
         <v>16.63</v>
@@ -1714,7 +1714,7 @@
         <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>6840387100</v>
+        <v>7096381575</v>
       </c>
       <c r="P14" t="n">
         <v>69200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 상승 및 FDA 승인 기대감 기반 주가 상승 전망.</t>
+          <t>미국 릴레이테라퓨틱스 상승, 간암 및 담관암 신약 FDA 승인 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FDA', '릴레이테라퓨틱스', '간암']</t>
+          <t>['신약', 'FDA', '승인']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>51</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>57967905575</v>
+        <v>60335412300</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1815,7 +1815,7 @@
         <v>15000</v>
       </c>
       <c r="R15" t="n">
-        <v>-463000</v>
+        <v>-496000</v>
       </c>
       <c r="S15" t="n">
         <v>-31000</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23200</v>
+        <v>23250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-2.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>64890968000</v>
+        <v>65857167250</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1943,123 +1943,123 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2770</v>
+        <v>48650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4</v>
+        <v>38.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2885</v>
+        <v>51200</v>
       </c>
       <c r="K17" t="n">
-        <v>3000</v>
+        <v>51600</v>
       </c>
       <c r="L17" t="n">
-        <v>3480</v>
+        <v>51600</v>
       </c>
       <c r="M17" t="n">
-        <v>2770</v>
+        <v>48600</v>
       </c>
       <c r="N17" t="n">
-        <v>0.48</v>
+        <v>38.44</v>
       </c>
       <c r="O17" t="n">
-        <v>19882929568</v>
+        <v>63315201700</v>
       </c>
       <c r="P17" t="n">
-        <v>4760</v>
+        <v>67300</v>
       </c>
       <c r="Q17" t="n">
-        <v>973</v>
+        <v>23150</v>
       </c>
       <c r="R17" t="n">
-        <v>-227000</v>
+        <v>-262000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
+          <t>LNG 플랜트 5조 수주에도 불구하고 주가 하락, 6개월 보유에 대한 회의감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유상증자', '공매도', '차트분석']</t>
+          <t>['LNG', '수주', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48650</v>
+        <v>81200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.98%</t>
+          <t>'-6.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>469</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>273</v>
       </c>
       <c r="G18" t="n">
-        <v>165</v>
+        <v>1370</v>
       </c>
       <c r="H18" t="n">
-        <v>38.34</v>
+        <v>23.03</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>51200</v>
+        <v>86500</v>
       </c>
       <c r="K18" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="L18" t="n">
-        <v>51600</v>
+        <v>86100</v>
       </c>
       <c r="M18" t="n">
-        <v>48600</v>
+        <v>80500</v>
       </c>
       <c r="N18" t="n">
-        <v>38.44</v>
+        <v>23.05</v>
       </c>
       <c r="O18" t="n">
-        <v>62071142725</v>
+        <v>188811948500</v>
       </c>
       <c r="P18" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-259000</v>
+        <v>-486000</v>
       </c>
       <c r="S18" t="n">
-        <v>-30000</v>
+        <v>-68000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 횡보에 대한 불만과 함께 추가 매수 의견 제시.</t>
+          <t>미국 원전 수주 확정에도 불구하고 하락세 지속, 외인/기관/연기금 매도.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['LNG', '원전']</t>
+          <t>['원전', 'SMR', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81050</v>
+        <v>2690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.30%</t>
+          <t>'-6.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>0.92</v>
       </c>
       <c r="E19" t="n">
-        <v>421</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>251</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>1260</v>
+        <v>151</v>
       </c>
       <c r="H19" t="n">
-        <v>23.03</v>
+        <v>1.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>86500</v>
+        <v>2885</v>
       </c>
       <c r="K19" t="n">
-        <v>86100</v>
+        <v>3000</v>
       </c>
       <c r="L19" t="n">
-        <v>86100</v>
+        <v>3480</v>
       </c>
       <c r="M19" t="n">
-        <v>80800</v>
+        <v>2690</v>
       </c>
       <c r="N19" t="n">
-        <v>23.05</v>
+        <v>0.48</v>
       </c>
       <c r="O19" t="n">
-        <v>172979943200</v>
+        <v>20517562933</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>4760</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>973</v>
       </c>
       <c r="R19" t="n">
-        <v>-474000</v>
+        <v>-227000</v>
       </c>
       <c r="S19" t="n">
-        <v>-68000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 2기 확정 소식에도 불구하고 주가 하락 및 매도세 관측.</t>
+          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '외인']</t>
+          <t>['유상증자', '공매도', '차트분석']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17400</v>
+        <v>17450</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.45%</t>
+          <t>'-7.18%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>551</v>
+        <v>597</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2260,13 +2260,13 @@
         <v>18800</v>
       </c>
       <c r="M20" t="n">
-        <v>17380</v>
+        <v>17370</v>
       </c>
       <c r="N20" t="n">
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>110241634480</v>
+        <v>112744130325</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2275,14 +2275,14 @@
         <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-1845000</v>
+        <v>-1898000</v>
       </c>
       <c r="S20" t="n">
         <v>-250000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 관련 언급 및 대차해지 운동 독려.</t>
+          <t>공매도 세력의 파산 가능성 언급과 대차 해지 운동 독려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지']</t>
+          <t>['공매도', '대차', '파산']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260923_11.xlsx
+++ b/data/trending_integrated_20260923_11.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31400819258</v>
+        <v>31411125428</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19040</v>
+        <v>18890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.11%</t>
+          <t>'+21.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16540</v>
+        <v>15520</v>
       </c>
       <c r="K3" t="n">
-        <v>17530</v>
+        <v>15800</v>
       </c>
       <c r="L3" t="n">
-        <v>19950</v>
+        <v>19150</v>
       </c>
       <c r="M3" t="n">
-        <v>17500</v>
+        <v>15200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>264476456375</v>
+        <v>69415584985</v>
       </c>
       <c r="P3" t="n">
-        <v>30550</v>
+        <v>34650</v>
       </c>
       <c r="Q3" t="n">
-        <v>6100</v>
+        <v>6980</v>
       </c>
       <c r="R3" t="n">
-        <v>-46000</v>
+        <v>2000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등, 양자 보안 기술의 상용화 가능성과 공매도 세력 언급.</t>
+          <t>스페이스X 및 NASA 선정, 인도발 수주 재료로 인한 초강세 랠리 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자', '보안', '공매도']</t>
+          <t>['스페이스X', 'NASA', '수주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17810</v>
+        <v>18880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.76%</t>
+          <t>'+14.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15520</v>
+        <v>16540</v>
       </c>
       <c r="K4" t="n">
-        <v>15800</v>
+        <v>17530</v>
       </c>
       <c r="L4" t="n">
-        <v>19050</v>
+        <v>19950</v>
       </c>
       <c r="M4" t="n">
-        <v>15200</v>
+        <v>17500</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>57126437100</v>
+        <v>268276381070</v>
       </c>
       <c r="P4" t="n">
-        <v>34650</v>
+        <v>30550</v>
       </c>
       <c r="Q4" t="n">
-        <v>6980</v>
+        <v>6100</v>
       </c>
       <c r="R4" t="n">
-        <v>2000</v>
+        <v>-46000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 11조원 휴대용 X-ray 시장 도전 및 인도발 수주 재료 부각.</t>
+          <t>양자 보안 관련 기술 부각 및 미국 시장 급등세 영향, 긍정적 주가 흐름 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['X-ray', '스페이스X', '수주']</t>
+          <t>['양자 보안', '미국 시장', '주가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14450</v>
+        <v>14530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.15%</t>
+          <t>'+11.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H5" t="n">
         <v>0.86</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>125757818165</v>
+        <v>127080259510</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3895</v>
+        <v>3890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.56%</t>
+          <t>'+4.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>57781000754</v>
+        <v>58741726294</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급격한 하락과 물량 떠넘기기 의혹, 상폐 및 단기 거래장에 대한 부정적 전망.</t>
+          <t>대규모 거래량 동반한 급락 후 투매 현상 발생, 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['급락', '물량', '단타']</t>
+          <t>['단타', '거래량', '투매']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217500</v>
+        <v>218000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H7" t="n">
         <v>75.51000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>598145385500</v>
+        <v>609026753250</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="G8" t="n">
-        <v>1926</v>
+        <v>1916</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1147,28 +1147,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>275000</v>
+        <v>276500</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>284500</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>281000</v>
       </c>
       <c r="N8" t="n">
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2372301000000</v>
+        <v>2442536419750</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>82400</v>
       </c>
       <c r="R8" t="n">
         <v>1744000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JP모건의 HBM 1위 인정, 개인 매도 자제 시 상승 전망.</t>
+          <t>HBM 시장 점유율 확대 기대감 속 개인 매수세 집중.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', '배당', '상승']</t>
+          <t>['HBM', '배당', '주주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13890</v>
+        <v>13850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.13%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H9" t="n">
         <v>9.609999999999999</v>
@@ -1254,7 +1254,7 @@
         <v>9.77</v>
       </c>
       <c r="O9" t="n">
-        <v>87871542715</v>
+        <v>88417079310</v>
       </c>
       <c r="P9" t="n">
         <v>23550</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8550</v>
+        <v>8510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>17629797400</v>
+        <v>18181851425</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리기판 사업 성장성 및 실적 개선 기대감, 외인 매수세 일부 유입.</t>
+          <t>유리 기판 사업 경쟁력 부각 및 실적 개선 전망에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '실적', '외인']</t>
+          <t>['유리 기판', '디스플레이', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1844000</v>
+        <v>1840000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>507</v>
       </c>
       <c r="G11" t="n">
-        <v>1668</v>
+        <v>1686</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>2709575745500</v>
+        <v>2804985321500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 전반에 대한 불신과 외인 매도세 언급, 마이크론과의 비교.</t>
+          <t>외국인 매도세 지속 및 반도체 시장 경쟁 심화 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국장', '외인', '반도체']</t>
+          <t>['반도체', '외인', '국장']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31450</v>
+        <v>31350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1507,7 +1507,7 @@
         <v>120</v>
       </c>
       <c r="H12" t="n">
-        <v>52.81</v>
+        <v>52.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>75692210125</v>
+        <v>77252702375</v>
       </c>
       <c r="P12" t="n">
         <v>32100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17600</v>
+        <v>17690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H13" t="n">
         <v>5.46</v>
@@ -1622,7 +1622,7 @@
         <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>115130435660</v>
+        <v>116491893105</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30650</v>
+        <v>30550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G14" t="n">
-        <v>1393</v>
+        <v>1468</v>
       </c>
       <c r="H14" t="n">
         <v>16.63</v>
@@ -1714,7 +1714,7 @@
         <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>7096381575</v>
+        <v>7320908125</v>
       </c>
       <c r="P14" t="n">
         <v>69200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30775</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>60335412300</v>
+        <v>61506586125</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23250</v>
+        <v>23200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F16" t="n">
         <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>65857167250</v>
+        <v>66036436675</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48650</v>
+        <v>48700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.98%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
         <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H17" t="n">
         <v>38.34</v>
@@ -1990,7 +1990,7 @@
         <v>38.44</v>
       </c>
       <c r="O17" t="n">
-        <v>63315201700</v>
+        <v>64971714300</v>
       </c>
       <c r="P17" t="n">
         <v>67300</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>LNG 플랜트 5조 수주에도 불구하고 주가 하락, 6개월 보유에 대한 회의감.</t>
+          <t>LNG 플랜트 수주에도 불구하고 주가 부진 및 단기 차익 실현 매물 출회.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG', '수주', '주가']</t>
+          <t>['LNG 플랜트', '수주', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,184 +2035,184 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>81200</v>
+        <v>2715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.13%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.92</v>
       </c>
       <c r="E18" t="n">
-        <v>469</v>
+        <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>1370</v>
+        <v>160</v>
       </c>
       <c r="H18" t="n">
-        <v>23.03</v>
+        <v>1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>86500</v>
+        <v>2885</v>
       </c>
       <c r="K18" t="n">
-        <v>86100</v>
+        <v>3000</v>
       </c>
       <c r="L18" t="n">
-        <v>86100</v>
+        <v>3480</v>
       </c>
       <c r="M18" t="n">
-        <v>80500</v>
+        <v>2685</v>
       </c>
       <c r="N18" t="n">
-        <v>23.05</v>
+        <v>0.48</v>
       </c>
       <c r="O18" t="n">
-        <v>188811948500</v>
+        <v>20772075158</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>4760</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>973</v>
       </c>
       <c r="R18" t="n">
-        <v>-486000</v>
+        <v>-227000</v>
       </c>
       <c r="S18" t="n">
-        <v>-68000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 수주 확정에도 불구하고 하락세 지속, 외인/기관/연기금 매도.</t>
+          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '하락']</t>
+          <t>['유상증자', '공매도', '차트분석']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2690</v>
+        <v>81100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.76%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.92</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>289</v>
       </c>
       <c r="G19" t="n">
-        <v>151</v>
+        <v>1443</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4</v>
+        <v>23.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2885</v>
+        <v>86500</v>
       </c>
       <c r="K19" t="n">
-        <v>3000</v>
+        <v>86100</v>
       </c>
       <c r="L19" t="n">
-        <v>3480</v>
+        <v>86100</v>
       </c>
       <c r="M19" t="n">
-        <v>2690</v>
+        <v>80500</v>
       </c>
       <c r="N19" t="n">
-        <v>0.48</v>
+        <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>20517562933</v>
+        <v>198982363450</v>
       </c>
       <c r="P19" t="n">
-        <v>4760</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>973</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-227000</v>
+        <v>-486000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-68000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
+          <t>미국 원전 수주 기대감에도 불구하고 주가 하락 및 외인, 기관 매도세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['유상증자', '공매도', '차트분석']</t>
+          <t>['원전', 'SMR', '주가조작']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17450</v>
+        <v>17480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.18%</t>
+          <t>'-7.02%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>112744130325</v>
+        <v>114355281450</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>

--- a/data/trending_integrated_20260923_11.xlsx
+++ b/data/trending_integrated_20260923_11.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31411125428</v>
+        <v>31476737933</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18890</v>
+        <v>18470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.71%</t>
+          <t>'+19.01%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>69415584985</v>
+        <v>73032584170</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 인도발 수주 재료로 인한 초강세 랠리 기대.</t>
+          <t>스페이스X, NASA 선정 등 강력한 신규 재료(포터블 X-Ray)가 부각되며 주가 상승 기대감이 높음. 인도 수주 및 공장 완공 등 구체적인 팩트 기반 정보와 함께 시가총액 1조원 돌파 가능성도 언급됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', '수주']</t>
+          <t>['스페이스X', 'NASA', 'X-Ray']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18880</v>
+        <v>15070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.15%</t>
+          <t>'+15.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16540</v>
+        <v>13000</v>
       </c>
       <c r="K4" t="n">
-        <v>17530</v>
+        <v>12870</v>
       </c>
       <c r="L4" t="n">
-        <v>19950</v>
+        <v>15900</v>
       </c>
       <c r="M4" t="n">
-        <v>17500</v>
+        <v>12650</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>268276381070</v>
+        <v>138388290475</v>
       </c>
       <c r="P4" t="n">
-        <v>30550</v>
+        <v>25700</v>
       </c>
       <c r="Q4" t="n">
-        <v>6100</v>
+        <v>4600</v>
       </c>
       <c r="R4" t="n">
-        <v>-46000</v>
+        <v>95000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자 보안 관련 기술 부각 및 미국 시장 급등세 영향, 긍정적 주가 흐름 전망.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자 보안', '미국 시장', '주가']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14530</v>
+        <v>18820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.77%</t>
+          <t>'+13.78%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.42</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13000</v>
+        <v>16540</v>
       </c>
       <c r="K5" t="n">
-        <v>12870</v>
+        <v>17530</v>
       </c>
       <c r="L5" t="n">
-        <v>15900</v>
+        <v>19950</v>
       </c>
       <c r="M5" t="n">
-        <v>12650</v>
+        <v>17500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>127080259510</v>
+        <v>269412528875</v>
       </c>
       <c r="P5" t="n">
-        <v>25700</v>
+        <v>30550</v>
       </c>
       <c r="Q5" t="n">
-        <v>4600</v>
+        <v>6100</v>
       </c>
       <c r="R5" t="n">
-        <v>95000</v>
+        <v>-46000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>양자 보안 관련 기술 부각 및 미국 시장 급등세 영향, 긍정적 주가 흐름 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['양자 보안', '미국 시장', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3890</v>
+        <v>3900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.43%</t>
+          <t>'+4.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>58741726294</v>
+        <v>60245578311</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대규모 거래량 동반한 급락 후 투매 현상 발생, 투자 심리 위축.</t>
+          <t>급격한 주가 하락과 함께 물량 떠넘기기, 상장 폐지 요구 등 강한 부정적 감정과 불만이 표출됨. 단타 위주의 시장으로 변질되었다는 의견도 나타남.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['단타', '거래량', '투매']</t>
+          <t>['주가 하락', '물량 떠넘기기', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218000</v>
+        <v>217500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="H7" t="n">
         <v>75.51000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>609026753250</v>
+        <v>639398631000</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>281750</v>
+        <v>13885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+2.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>1916</v>
+        <v>192</v>
       </c>
       <c r="H8" t="n">
-        <v>46.55</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276500</v>
+        <v>13600</v>
       </c>
       <c r="K8" t="n">
-        <v>284500</v>
+        <v>13750</v>
       </c>
       <c r="L8" t="n">
-        <v>285000</v>
+        <v>15050</v>
       </c>
       <c r="M8" t="n">
-        <v>281000</v>
+        <v>13740</v>
       </c>
       <c r="N8" t="n">
-        <v>46.56</v>
+        <v>9.77</v>
       </c>
       <c r="O8" t="n">
-        <v>2442536419750</v>
+        <v>89127189210</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>82400</v>
+        <v>5780</v>
       </c>
       <c r="R8" t="n">
-        <v>1744000</v>
+        <v>180000</v>
       </c>
       <c r="S8" t="n">
-        <v>499000</v>
+        <v>-194000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HBM 시장 점유율 확대 기대감 속 개인 매수세 집중.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', '배당', '주주']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13850</v>
+        <v>281750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>476</v>
       </c>
       <c r="G9" t="n">
-        <v>189</v>
+        <v>1925</v>
       </c>
       <c r="H9" t="n">
-        <v>9.609999999999999</v>
+        <v>46.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13600</v>
+        <v>276500</v>
       </c>
       <c r="K9" t="n">
-        <v>13750</v>
+        <v>284500</v>
       </c>
       <c r="L9" t="n">
-        <v>15050</v>
+        <v>285000</v>
       </c>
       <c r="M9" t="n">
-        <v>13740</v>
+        <v>281000</v>
       </c>
       <c r="N9" t="n">
-        <v>9.77</v>
+        <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>88417079310</v>
+        <v>2486871245000</v>
       </c>
       <c r="P9" t="n">
-        <v>23550</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>5780</v>
+        <v>82400</v>
       </c>
       <c r="R9" t="n">
-        <v>180000</v>
+        <v>1744000</v>
       </c>
       <c r="S9" t="n">
-        <v>-194000</v>
+        <v>499000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>대통령 및 정당 관련 정치적 언급과 함께 주가 상승 및 보유를 독려하는 의견이 혼재함. 단기적 주가 상승 기대 및 보유 의견이 있으나, 명확한 팩트 기반 근거는 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['정치', '주가 상승', '보유']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8510</v>
+        <v>8530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>18181851425</v>
+        <v>18743084015</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리 기판 사업 경쟁력 부각 및 실적 개선 전망에 따른 주가 상승 기대.</t>
+          <t>실적 개선 및 초저가에 대한 기대와 함께 유리 기판, FLiPP 등 신규 사업 언급이 있으나, 적자 지속, 높은 부채, 목표 주가 하향 등에 대한 부정적 의견이 강하게 나타남. 분석 리포트의 신뢰성에 대한 의문 제기도 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리 기판', '디스플레이', '실적']</t>
+          <t>['실적', '유리 기판', '부채']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1840000</v>
+        <v>1841000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="G11" t="n">
-        <v>1686</v>
+        <v>1668</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1432,13 +1432,13 @@
         <v>1900000</v>
       </c>
       <c r="M11" t="n">
-        <v>1837000</v>
+        <v>1836000</v>
       </c>
       <c r="N11" t="n">
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>2804985321500</v>
+        <v>2912777748000</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 반도체 시장 경쟁 심화 우려.</t>
+          <t>한국 주식 시장 전반의 신뢰도 하락과 조작 의혹이 강하게 제기되며, SK하이닉스에 대한 직접적인 언급은 미미함. 반도체 업황 및 미국 주식과의 비교를 통해 부정적 인식이 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외인', '국장']</t>
+          <t>['국장', '신뢰도', '조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1504,10 +1504,10 @@
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" t="n">
-        <v>52.8</v>
+        <v>52.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>77252702375</v>
+        <v>78937040425</v>
       </c>
       <c r="P12" t="n">
         <v>32100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17690</v>
+        <v>17680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="H13" t="n">
         <v>5.46</v>
@@ -1622,7 +1622,7 @@
         <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>116491893105</v>
+        <v>117787929995</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감 및 개인/외국인 매수세 전환 가능성 언급.</t>
+          <t>추석 연휴 전 주가 상승에 대한 기대감과 함께 2만원 돌파를 독려하는 의견이 나타남. 쇼티지 현상, 외국인/개인 매수 전환 가능성 등 긍정적 요소를 언급하나, 명절 전 주가 하락 가능성도 제기됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['쇼티지', '광섬유']</t>
+          <t>['추석', '주가 상승', '쇼티지']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F14" t="n">
         <v>158</v>
       </c>
       <c r="G14" t="n">
-        <v>1468</v>
+        <v>1497</v>
       </c>
       <c r="H14" t="n">
         <v>16.63</v>
@@ -1714,7 +1714,7 @@
         <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>7320908125</v>
+        <v>7446133825</v>
       </c>
       <c r="P14" t="n">
         <v>69200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1800,13 +1800,13 @@
         <v>32200</v>
       </c>
       <c r="M15" t="n">
-        <v>30650</v>
+        <v>30550</v>
       </c>
       <c r="N15" t="n">
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>61506586125</v>
+        <v>63738768425</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1866,13 +1866,13 @@
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>66036436675</v>
+        <v>66253109975</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 '세계 최고 헬스테크 기업' 선정. 10만까지 상승 기대감 있으나 프로그램 매매 및 눌림목 언급.</t>
+          <t>타임지 선정 '세계 최고 헬스테크 기업'이라는 긍정적 뉴스를 기반으로 주가 상승 기대감이 있으나, 실제 주가 움직임에 대한 실망감과 변동성에 대한 언급도 나타남. 보유 및 기다림을 강조하는 의견이 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '프로그램매매']</t>
+          <t>['헬스테크', '타임지', '주가 상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48700</v>
+        <v>48650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H17" t="n">
         <v>38.34</v>
@@ -1990,7 +1990,7 @@
         <v>38.44</v>
       </c>
       <c r="O17" t="n">
-        <v>64971714300</v>
+        <v>66613404175</v>
       </c>
       <c r="P17" t="n">
         <v>67300</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>LNG 플랜트 수주에도 불구하고 주가 부진 및 단기 차익 실현 매물 출회.</t>
+          <t>5조원 수주에도 불구하고 주가 상승이 미미하다는 불만과 함께, 주가 조작 및 하락에 대한 부정적 전망이 지배적임. 6개월간 보유한 투자자들의 좌절감이 드러남.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG 플랜트', '수주', '주가']</t>
+          <t>['수주', '주가 조작', '하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2715</v>
+        <v>2740</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.89%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.92</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H18" t="n">
         <v>1.4</v>
@@ -2082,7 +2082,7 @@
         <v>0.48</v>
       </c>
       <c r="O18" t="n">
-        <v>20772075158</v>
+        <v>21062583604</v>
       </c>
       <c r="P18" t="n">
         <v>4760</v>
@@ -2142,13 +2142,13 @@
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="F19" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G19" t="n">
-        <v>1443</v>
+        <v>1496</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2174,7 +2174,7 @@
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>198982363450</v>
+        <v>212453462050</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 수주 기대감에도 불구하고 주가 하락 및 외인, 기관 매도세.</t>
+          <t>미국 원전 수주 기대감과 함께 소형SMR, 트럼프 관련 언급이 있으나, 주가 하락 및 차트 붕괴에 대한 부정적 전망과 외인/기관 매도에 대한 불만이 주를 이룸. 감정적 표현과 불확실한 정보가 혼재함.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가조작']</t>
+          <t>['원전', 'SMR', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17480</v>
+        <v>17570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.02%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G20" t="n">
-        <v>620</v>
+        <v>662</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>114355281450</v>
+        <v>116494851575</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 가능성 언급과 대차 해지 운동 독려.</t>
+          <t>공매도 세력의 파산과 관련된 강력한 주장이 반복적으로 나타나며, 대차해지 운동 동참을 촉구함. 감사원 신고, 금융 당국 수사 언급 등 일부 사실 기반 주장이 있으나, 감정적이고 선동적인 어조가 강함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '파산']</t>
+          <t>['공매도', '대차해지', '파산']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260923_11.xlsx
+++ b/data/trending_integrated_20260923_11.xlsx
@@ -584,7 +584,7 @@
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31476737933</v>
+        <v>31488576683</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18470</v>
+        <v>18490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.01%</t>
+          <t>'+19.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>121</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>73032584170</v>
+        <v>74634962050</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X, NASA 선정 등 강력한 신규 재료(포터블 X-Ray)가 부각되며 주가 상승 기대감이 높음. 인도 수주 및 공장 완공 등 구체적인 팩트 기반 정보와 함께 시가총액 1조원 돌파 가능성도 언급됨.</t>
+          <t>NASA 및 스페이스X 선정, 인도발 수주 등 강력한 호재 기반의 상승 기대감. 11조원 포터블 X-Ray 시장 도전 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', 'X-Ray']</t>
+          <t>['NASA', '스페이스X', '포터블 X-Ray']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15070</v>
+        <v>14910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.92%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
         <v>0.86</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>138388290475</v>
+        <v>144815905255</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18820</v>
+        <v>18840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.78%</t>
+          <t>'+13.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>269412528875</v>
+        <v>270861590475</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>양자 보안 관련 기술 부각 및 미국 시장 급등세 영향, 긍정적 주가 흐름 전망.</t>
+          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 장비 언급. 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자 보안', '미국 시장', '주가']</t>
+          <t>['양자 보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3900</v>
+        <v>3880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.70%</t>
+          <t>'+4.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>60245578311</v>
+        <v>60655958801</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급격한 주가 하락과 함께 물량 떠넘기기, 상장 폐지 요구 등 강한 부정적 감정과 불만이 표출됨. 단타 위주의 시장으로 변질되었다는 의견도 나타남.</t>
+          <t>주가 하락 및 물량 떠넘기기에 대한 불만. 상장 폐지 가능성 언급 및 단기적인 거래량 급증에 대한 경계.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 하락', '물량 떠넘기기', '단타']</t>
+          <t>['물량 떠넘기기', '상장 폐지', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217500</v>
+        <v>13960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="H7" t="n">
-        <v>75.51000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>13600</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>220000</v>
+        <v>15050</v>
       </c>
       <c r="M7" t="n">
-        <v>216500</v>
+        <v>13740</v>
       </c>
       <c r="N7" t="n">
-        <v>75.5</v>
+        <v>9.77</v>
       </c>
       <c r="O7" t="n">
-        <v>639398631000</v>
+        <v>90230924300</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>23550</v>
       </c>
       <c r="Q7" t="n">
-        <v>65000</v>
+        <v>5780</v>
       </c>
       <c r="R7" t="n">
-        <v>753000</v>
+        <v>180000</v>
       </c>
       <c r="S7" t="n">
-        <v>-47000</v>
+        <v>-194000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '장기보유']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13885</v>
+        <v>217000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.10%</t>
+          <t>'+2.60%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.16</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>192</v>
+        <v>294</v>
       </c>
       <c r="H8" t="n">
-        <v>9.609999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13600</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>13750</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>15050</v>
+        <v>220000</v>
       </c>
       <c r="M8" t="n">
-        <v>13740</v>
+        <v>216500</v>
       </c>
       <c r="N8" t="n">
-        <v>9.77</v>
+        <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>89127189210</v>
+        <v>646349067500</v>
       </c>
       <c r="P8" t="n">
-        <v>23550</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>5780</v>
+        <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>180000</v>
+        <v>753000</v>
       </c>
       <c r="S8" t="n">
-        <v>-194000</v>
+        <v>-47000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['배당', '우선주', '장기보유']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>281750</v>
+        <v>282000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.90%</t>
+          <t>'+1.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G9" t="n">
-        <v>1925</v>
+        <v>1917</v>
       </c>
       <c r="H9" t="n">
         <v>46.55</v>
@@ -1254,7 +1254,7 @@
         <v>46.56</v>
       </c>
       <c r="O9" t="n">
-        <v>2486871245000</v>
+        <v>2551440088000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8530</v>
+        <v>8520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>18743084015</v>
+        <v>19010793495</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>실적 개선 및 초저가에 대한 기대와 함께 유리 기판, FLiPP 등 신규 사업 언급이 있으나, 적자 지속, 높은 부채, 목표 주가 하향 등에 대한 부정적 의견이 강하게 나타남. 분석 리포트의 신뢰성에 대한 의문 제기도 있음.</t>
+          <t>실적 개선 및 주가 상승 기대감과 함께, 일부 애널리스트의 부정적인 목표주가 하향 분석 및 가짜 외인 매도에 대한 의혹 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '유리 기판', '부채']</t>
+          <t>['실적 개선', '목표주가', '가짜 외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1841000</v>
+        <v>1844000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.05%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G11" t="n">
-        <v>1668</v>
+        <v>1653</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>2912777748000</v>
+        <v>2995654512500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>한국 주식 시장 전반의 신뢰도 하락과 조작 의혹이 강하게 제기되며, SK하이닉스에 대한 직접적인 언급은 미미함. 반도체 업황 및 미국 주식과의 비교를 통해 부정적 인식이 나타남.</t>
+          <t>국내 증시의 신뢰도 부족과 주가 조작 의혹 제기. 미국 반도체 시장과의 비교 및 외인 투자자 동향에 대한 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국장', '신뢰도', '조작']</t>
+          <t>['국내 증시', '신뢰도', '주가 조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H12" t="n">
         <v>52.81</v>
@@ -1530,7 +1530,7 @@
         <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>78937040425</v>
+        <v>79878175550</v>
       </c>
       <c r="P12" t="n">
         <v>32100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17680</v>
+        <v>17700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>652</v>
+        <v>703</v>
       </c>
       <c r="H13" t="n">
         <v>5.46</v>
@@ -1622,7 +1622,7 @@
         <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>117787929995</v>
+        <v>118998735135</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30550</v>
+        <v>30700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F14" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G14" t="n">
-        <v>1497</v>
+        <v>1521</v>
       </c>
       <c r="H14" t="n">
         <v>16.63</v>
@@ -1714,7 +1714,7 @@
         <v>16.42</v>
       </c>
       <c r="O14" t="n">
-        <v>7446133825</v>
+        <v>7565364275</v>
       </c>
       <c r="P14" t="n">
         <v>69200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 상승, 간암 및 담관암 신약 FDA 승인 기대감.</t>
+          <t>미국 FDA 신약 승인 기대감 및 간암, 담관암 관련 긍정적 전망. 릴레이테라퓨틱스 상승 및 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', '승인']</t>
+          <t>['신약 승인', 'FDA', '간암']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>30800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
         <v>112</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>63738768425</v>
+        <v>64390438625</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1866,13 +1866,13 @@
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>66253109975</v>
+        <v>66463056800</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48650</v>
+        <v>48750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.98%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H17" t="n">
         <v>38.34</v>
@@ -1990,7 +1990,7 @@
         <v>38.44</v>
       </c>
       <c r="O17" t="n">
-        <v>66613404175</v>
+        <v>67706166950</v>
       </c>
       <c r="P17" t="n">
         <v>67300</v>
@@ -2050,13 +2050,13 @@
         <v>0.92</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
         <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H18" t="n">
         <v>1.4</v>
@@ -2082,7 +2082,7 @@
         <v>0.48</v>
       </c>
       <c r="O18" t="n">
-        <v>21062583604</v>
+        <v>21126483169</v>
       </c>
       <c r="P18" t="n">
         <v>4760</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유상증자 및 배정 관련 이슈, 3700원 돌파 여부 주목. 공매도 세력 활동 가능성 언급.</t>
+          <t>유상증자 및 경영권 변경에 대한 우려. 차트 분석 및 주가 흐름에 대한 언급. 투자자들의 신중한 접근 당부.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유상증자', '공매도', '차트분석']</t>
+          <t>['유상증자', '경영권 변경', '차트 분석']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81100</v>
+        <v>81500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-5.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="F19" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="G19" t="n">
-        <v>1496</v>
+        <v>1541</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2162,25 +2162,25 @@
         <v>86500</v>
       </c>
       <c r="K19" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>80500</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>212453462050</v>
+        <v>220201000000</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>-486000</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17570</v>
+        <v>17610</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F20" t="n">
         <v>103</v>
       </c>
       <c r="G20" t="n">
-        <v>662</v>
+        <v>758</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>116494851575</v>
+        <v>118116847515</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산과 관련된 강력한 주장이 반복적으로 나타나며, 대차해지 운동 동참을 촉구함. 감사원 신고, 금융 당국 수사 언급 등 일부 사실 기반 주장이 있으나, 감정적이고 선동적인 어조가 강함.</t>
+          <t>공매도 세력에 대한 부정적인 인식과 함께 대차 해지 운동 참여 독려. 공매도 파산 주장.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '파산']</t>
+          <t>['공매도', '대차 해지', '파산']</t>
         </is>
       </c>
       <c r="X20" t="n">
